--- a/docs/downloads/09/t8_transition_marovoay_ampijoroa.xlsx
+++ b/docs/downloads/09/t8_transition_marovoay_ampijoroa.xlsx
@@ -512,12 +512,6 @@
           <t>Tubercule+Céréale</t>
         </is>
       </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -534,12 +528,6 @@
         <is>
           <t>Patate douce</t>
         </is>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>1.5</v>
       </c>
     </row>
     <row r="9">
